--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\eoe\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB01465-CC4D-451F-B9E7-B5F9D56E1871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9D37B2-6B61-4F66-B02A-C31EEF6C1C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>id</t>
   </si>
@@ -55,6 +55,18 @@
   </si>
   <si>
     <t>deathAudioClipName</t>
+  </si>
+  <si>
+    <t>attackRange</t>
+  </si>
+  <si>
+    <t>knockbackResistance</t>
+  </si>
+  <si>
+    <t>attackCooldown</t>
+  </si>
+  <si>
+    <t>gold</t>
   </si>
 </sst>
 </file>
@@ -97,12 +109,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -366,17 +375,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DC884F-D038-4541-88D7-B9764BF74C8A}">
-  <dimension ref="A1:J2"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="5" width="15.6328125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="15.6328125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.26953125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="19.90625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6328125" style="1" customWidth="1"/>
+    <col min="1" max="7" width="15.6328125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="17.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6328125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="23.90625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="25.26953125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="19.90625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="15.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -392,20 +406,32 @@
       <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -421,15 +447,27 @@
       <c r="E2" s="1">
         <v>5</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="1">
         <v>0.3</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="1">
         <v>1.5</v>
+      </c>
+      <c r="H2" s="1">
+        <v>1</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="43" fitToHeight="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\eoe\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD9D37B2-6B61-4F66-B02A-C31EEF6C1C90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAD807A-681D-466C-9CA0-63F8AD034C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -381,7 +381,9 @@
   <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="7" width="15.6328125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" style="1" customWidth="1"/>
+    <col min="3" max="7" width="15.6328125" style="1" customWidth="1"/>
     <col min="8" max="8" width="17.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.6328125" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.90625" style="1" bestFit="1" customWidth="1"/>

--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\eoe\Assets\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AAD807A-681D-466C-9CA0-63F8AD034C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0044399-B7A1-4F46-B8BC-2EF185EE4B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>id</t>
   </si>
@@ -49,12 +49,6 @@
   </si>
   <si>
     <t>prefabName</t>
-  </si>
-  <si>
-    <t>deathVfxName</t>
-  </si>
-  <si>
-    <t>deathAudioClipName</t>
   </si>
   <si>
     <t>attackRange</t>
@@ -378,7 +372,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.6328125" style="1" customWidth="1"/>
@@ -387,12 +381,10 @@
     <col min="8" max="8" width="17.81640625" style="1" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.6328125" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="25.26953125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="19.90625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="15.6328125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="15.6328125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -415,25 +407,19 @@
         <v>5</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>1001</v>
       </c>
@@ -464,7 +450,7 @@
       <c r="J2" s="1">
         <v>1</v>
       </c>
-      <c r="M2" s="1">
+      <c r="K2" s="1">
         <v>5</v>
       </c>
     </row>

--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -1,21 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\Idle-rpg\eoe\Assets\Excels\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0044399-B7A1-4F46-B8BC-2EF185EE4B30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc" lowestEdited="7"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11620" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="monsters" sheetId="2" r:id="rId1"/>
+    <sheet name="monsters" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -27,53 +22,71 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>health</t>
-  </si>
-  <si>
-    <t>attack</t>
-  </si>
-  <si>
-    <t>exp</t>
-  </si>
-  <si>
-    <t>moveSpeed</t>
-  </si>
-  <si>
-    <t>stopDistance</t>
-  </si>
-  <si>
-    <t>monster.1001</t>
-  </si>
-  <si>
-    <t>prefabName</t>
-  </si>
-  <si>
-    <t>attackRange</t>
-  </si>
-  <si>
-    <t>knockbackResistance</t>
-  </si>
-  <si>
-    <t>attackCooldown</t>
-  </si>
-  <si>
-    <t>gold</t>
+    <t xml:space="preserve">id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">prefabName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">health</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">exp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">moveSpeed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stopDistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attackCooldown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">attackRange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">knockbackResistance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">monster.1001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="13"/>
@@ -92,7 +105,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -100,101 +113,54 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFEAD1DC"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF99CC00"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF333333"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -236,14 +202,14 @@
     </a:clrScheme>
     <a:fontScheme name="Sheets">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:cs typeface="Arial" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -273,7 +239,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -297,7 +263,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -357,57 +323,55 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17DC884F-D038-4541-88D7-B9764BF74C8A}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="true"/>
   </sheetPr>
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="15.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" style="1" customWidth="1"/>
-    <col min="3" max="7" width="15.6328125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="17.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.6328125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="23.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.6328125" style="1" customWidth="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.63"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.63"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>8</v>
@@ -416,46 +380,51 @@
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="1">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="C2" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E2" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F2" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="H2" s="1">
+      <c r="F2" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="I2" s="1">
+      <c r="I2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="1" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="43" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -143,7 +143,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -406,7 +406,7 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" s="1" t="n">
         <v>2</v>

--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -1,111 +1,63 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="monsters" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="monsters" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prefabName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">health</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">exp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moveSpeed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">stopDistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attackCooldown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">attackRange</t>
-  </si>
-  <si>
-    <t xml:space="preserve">knockbackResistance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">monster.1001</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="5">
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+      <sz val="10"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <charset val="1"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
       <sz val="13"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
@@ -113,49 +65,104 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
+    <cellStyle name="Currency" xfId="3" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
+    <cellStyle name="Percent" xfId="5" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -332,99 +339,194 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr filterMode="0">
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="15.63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23.91"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="15.63"/>
+    <col width="15.63" customWidth="1" style="2" min="1" max="1"/>
+    <col width="18.45" customWidth="1" style="2" min="2" max="2"/>
+    <col width="15.63" customWidth="1" style="2" min="3" max="7"/>
+    <col width="17.82" customWidth="1" style="2" min="8" max="8"/>
+    <col width="15.63" customWidth="1" style="2" min="9" max="9"/>
+    <col width="23.91" customWidth="1" style="2" min="10" max="10"/>
+    <col width="15.63" customWidth="1" style="2" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="16.5" customHeight="1" s="3">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>prefabName</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>health</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>exp</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>moveSpeed</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>stopDistance</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>attackCooldown</t>
+        </is>
+      </c>
+      <c r="I1" s="2" t="inlineStr">
+        <is>
+          <t>attackRange</t>
+        </is>
+      </c>
+      <c r="J1" s="2" t="inlineStr">
+        <is>
+          <t>knockbackResistance</t>
+        </is>
+      </c>
+      <c r="K1" s="2" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16.5" customHeight="1" s="3">
+      <c r="A2" s="2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>monster.1001</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="K2" s="2" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>monster.1002</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>7</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>monster.1003</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>28</v>
+      </c>
+      <c r="D4" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="E4" t="n">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="16.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="1" t="n">
+      <c r="F4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
         <v>10</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" s="1" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="G2" s="1" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="H2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="I2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="J2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="0" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup orientation="portrait" paperSize="1" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
 </file>
--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -344,7 +344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15.63" customWidth="1" style="2" min="1" max="1"/>
@@ -412,6 +412,16 @@
           <t>gold</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>rank</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>skills</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" s="3">
       <c r="A2" s="2" t="n">
@@ -449,79 +459,109 @@
       <c r="K2" s="2" t="n">
         <v>5</v>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>1002</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>monster.1002</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3" s="0" t="n">
         <v>0.9</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" s="0" t="n">
         <v>0.8</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" s="0" t="n">
         <v>7</v>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Elite</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>[{"skillId":2002,"cooldown":4.0,"damageMultiplier":1.5}]</t>
+        </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="n">
+      <c r="A4" s="0" t="n">
         <v>1003</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>monster.1003</t>
         </is>
       </c>
-      <c r="C4" t="n">
+      <c r="C4" s="0" t="n">
         <v>28</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="0" t="n">
         <v>0.5</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4" s="0" t="n">
         <v>0.7</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="0" t="n">
         <v>2.5</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" s="0" t="n">
         <v>10</v>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Boss</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>[{"skillId":2005,"cooldown":5.0,"damageMultiplier":2.0},{"skillId":2006,"cooldown":7.0,"damageMultiplier":1.25},{"skillId":2007,"cooldown":6.0,"damageMultiplier":1.0}]</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -394,7 +394,7 @@
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>attackCooldown</t>
+          <t>damageCooldown</t>
         </is>
       </c>
       <c r="I1" s="2" t="inlineStr">
@@ -412,12 +412,12 @@
           <t>gold</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="0" t="inlineStr">
         <is>
           <t>rank</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="0" t="inlineStr">
         <is>
           <t>skills</t>
         </is>
@@ -448,7 +448,7 @@
         <v>0.5</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I2" s="2" t="n">
         <v>2</v>
@@ -459,12 +459,12 @@
       <c r="K2" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="0" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="0" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
@@ -495,7 +495,7 @@
         <v>0.5</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I3" s="0" t="n">
         <v>2</v>
@@ -506,12 +506,12 @@
       <c r="K3" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="L3" s="0" t="inlineStr">
         <is>
           <t>Elite</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="M3" s="0" t="inlineStr">
         <is>
           <t>[{"skillId":2002,"cooldown":4.0,"damageMultiplier":1.5}]</t>
         </is>
@@ -542,7 +542,7 @@
         <v>0.7</v>
       </c>
       <c r="H4" s="0" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="I4" s="0" t="n">
         <v>2</v>
@@ -553,12 +553,12 @@
       <c r="K4" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="L4" s="0" t="inlineStr">
         <is>
           <t>Boss</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="M4" s="0" t="inlineStr">
         <is>
           <t>[{"skillId":2005,"cooldown":5.0,"damageMultiplier":2.0},{"skillId":2006,"cooldown":7.0,"damageMultiplier":1.25},{"skillId":2007,"cooldown":6.0,"damageMultiplier":1.0}]</t>
         </is>

--- a/eoe/Assets/Excels/MonsterConfig.xlsx
+++ b/eoe/Assets/Excels/MonsterConfig.xlsx
@@ -344,7 +344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:N4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="16.5" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="15.63" customWidth="1" style="2" min="1" max="1"/>
@@ -422,6 +422,11 @@
           <t>skills</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>statusResistances</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="16.5" customHeight="1" s="3">
       <c r="A2" s="2" t="n">
@@ -469,6 +474,11 @@
           <t>[]</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>[{"type":1,"resistance":0.0},{"type":2,"resistance":0.0},{"type":3,"resistance":0.0},{"type":4,"resistance":0.0}]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
@@ -516,6 +526,11 @@
           <t>[{"skillId":2002,"cooldown":4.0,"damageMultiplier":1.5}]</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>[{"type":1,"resistance":0.25},{"type":2,"resistance":0.2},{"type":3,"resistance":0.35},{"type":4,"resistance":0.25}]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
@@ -561,6 +576,11 @@
       <c r="M4" s="0" t="inlineStr">
         <is>
           <t>[{"skillId":2005,"cooldown":5.0,"damageMultiplier":2.0},{"skillId":2006,"cooldown":7.0,"damageMultiplier":1.25},{"skillId":2007,"cooldown":6.0,"damageMultiplier":1.0}]</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>[{"type":1,"resistance":0.5},{"type":2,"resistance":0.4},{"type":3,"resistance":0.6},{"type":4,"resistance":0.5}]</t>
         </is>
       </c>
     </row>
